--- a/AI_portfolio.xlsx
+++ b/AI_portfolio.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25980CED-52D0-4232-9555-54ABEEFD5A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B6A6BD-CEB8-4CC3-91D4-4F34683000E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5DF95D75-B56A-4A28-A4FD-98A7C607935C}"/>
   </bookViews>
   <sheets>
     <sheet name="Total" sheetId="4" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Total!$A$1:$M$28</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
   <extLst>
@@ -37,10 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="86">
-  <si>
-    <t>Nuværende eksponering</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="84">
   <si>
     <t>Danske Bank A/S</t>
   </si>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t>Vestas Wind System</t>
-  </si>
-  <si>
-    <t>Gevinst</t>
   </si>
   <si>
     <t>Frontline PLC</t>
@@ -675,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD91B5D-5949-4A3E-9EBC-E276EA4CC067}">
-  <dimension ref="A1:T32"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
@@ -691,66 +688,58 @@
     <col min="11" max="11" width="15.26953125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.7265625" customWidth="1"/>
-    <col min="20" max="20" width="8.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <v>47</v>
@@ -767,27 +756,21 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M2" t="s">
-        <v>40</v>
-      </c>
-      <c r="S2" s="1">
-        <v>29847.444000000003</v>
-      </c>
-      <c r="T2" s="1">
-        <v>3220.1862000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D3">
         <v>50</v>
@@ -804,27 +787,21 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M3" t="s">
-        <v>40</v>
-      </c>
-      <c r="S3" s="1">
-        <v>30825</v>
-      </c>
-      <c r="T3" s="1">
-        <v>9001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -841,27 +818,21 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M4" t="s">
-        <v>40</v>
-      </c>
-      <c r="S4" s="1">
-        <v>57879.7</v>
-      </c>
-      <c r="T4" s="1">
-        <v>20038.71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D5">
         <v>153</v>
@@ -878,27 +849,21 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M5" t="s">
-        <v>40</v>
-      </c>
-      <c r="S5" s="1">
-        <v>55998</v>
-      </c>
-      <c r="T5" s="1">
-        <v>25373.52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D6">
         <v>22</v>
@@ -915,27 +880,21 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M6" t="s">
-        <v>40</v>
-      </c>
-      <c r="S6" s="1">
-        <v>10906.942800000001</v>
-      </c>
-      <c r="T6" s="1">
-        <v>-863.51459999999679</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D7">
         <v>14</v>
@@ -952,27 +911,21 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M7" t="s">
-        <v>40</v>
-      </c>
-      <c r="S7" s="1">
-        <v>36407</v>
-      </c>
-      <c r="T7" s="1">
-        <v>-3961.0815999999977</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D8">
         <v>63</v>
@@ -989,27 +942,21 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M8" t="s">
-        <v>40</v>
-      </c>
-      <c r="S8" s="1">
-        <v>57739.5</v>
-      </c>
-      <c r="T8" s="1">
-        <v>32181.66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D9">
         <v>436</v>
@@ -1026,27 +973,21 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M9" t="s">
-        <v>40</v>
-      </c>
-      <c r="S9" s="1">
-        <v>140130</v>
-      </c>
-      <c r="T9" s="1">
-        <v>-53194.98000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D10">
         <v>38</v>
@@ -1063,27 +1004,21 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M10" t="s">
-        <v>40</v>
-      </c>
-      <c r="S10" s="1">
-        <v>28864.799999999999</v>
-      </c>
-      <c r="T10" s="1">
-        <v>4863.619999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D11">
         <v>9</v>
@@ -1100,27 +1035,21 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M11" t="s">
-        <v>40</v>
-      </c>
-      <c r="S11" s="1">
-        <v>10564.122599999999</v>
-      </c>
-      <c r="T11" s="1">
-        <v>923.47469999999885</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D12">
         <v>14</v>
@@ -1137,27 +1066,21 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M12" t="s">
-        <v>40</v>
-      </c>
-      <c r="S12" s="1">
-        <v>43557.334800000004</v>
-      </c>
-      <c r="T12" s="1">
-        <v>472.25080000000162</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -1174,27 +1097,21 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M13" t="s">
-        <v>40</v>
-      </c>
-      <c r="S13" s="1">
-        <v>22694.191999999999</v>
-      </c>
-      <c r="T13" s="1">
-        <v>3116.4392000000007</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14">
         <v>108</v>
@@ -1211,27 +1128,21 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M14" t="s">
-        <v>40</v>
-      </c>
-      <c r="S14" s="1">
-        <v>19315.8</v>
-      </c>
-      <c r="T14" s="1">
-        <v>3565.0799999999981</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D15">
         <v>25</v>
@@ -1248,27 +1159,21 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M15" t="s">
-        <v>40</v>
-      </c>
-      <c r="S15" s="1">
-        <v>10030.5</v>
-      </c>
-      <c r="T15" s="1">
-        <v>-1266.8150000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D16">
         <v>59</v>
@@ -1285,27 +1190,21 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M16" t="s">
-        <v>40</v>
-      </c>
-      <c r="S16" s="1">
-        <v>20165.02</v>
-      </c>
-      <c r="T16" s="1">
-        <v>1095.925</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D17">
         <v>52</v>
@@ -1322,27 +1221,21 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M17" t="s">
-        <v>40</v>
-      </c>
-      <c r="S17" s="1">
-        <v>8499.92</v>
-      </c>
-      <c r="T17" s="1">
-        <v>-2704.52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D18">
         <v>185</v>
@@ -1359,27 +1252,21 @@
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
       <c r="L18" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M18" t="s">
-        <v>40</v>
-      </c>
-      <c r="S18" s="1">
-        <v>12370.949999999999</v>
-      </c>
-      <c r="T18" s="1">
-        <v>-2199.2799999999993</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D19">
         <v>413</v>
@@ -1396,27 +1283,21 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M19" t="s">
-        <v>40</v>
-      </c>
-      <c r="S19" s="1">
-        <v>55234.619999999995</v>
-      </c>
-      <c r="T19" s="1">
-        <v>25714.784200000002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1433,27 +1314,21 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M20" t="s">
-        <v>40</v>
-      </c>
-      <c r="S20" s="1">
-        <v>14964.019999999999</v>
-      </c>
-      <c r="T20" s="1">
-        <v>-1151.8060300000009</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D21">
         <v>154</v>
@@ -1470,27 +1345,21 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M21" t="s">
-        <v>40</v>
-      </c>
-      <c r="S21" s="1">
-        <v>9153.76</v>
-      </c>
-      <c r="T21" s="1">
-        <v>-734.58923999999934</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D22">
         <v>44</v>
@@ -1507,27 +1376,21 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M22" t="s">
-        <v>40</v>
-      </c>
-      <c r="S22" s="1">
-        <v>16672.919999999998</v>
-      </c>
-      <c r="T22" s="1">
-        <v>-2000.7503999999988</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D23">
         <v>47</v>
@@ -1544,27 +1407,21 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M23" t="s">
-        <v>40</v>
-      </c>
-      <c r="S23" s="1">
-        <v>8381.0399999999991</v>
-      </c>
-      <c r="T23" s="1">
-        <v>-1387.0621200000003</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D24">
         <v>161</v>
@@ -1581,27 +1438,21 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M24" t="s">
-        <v>40</v>
-      </c>
-      <c r="S24" s="1">
-        <v>14354.76</v>
-      </c>
-      <c r="T24" s="1">
-        <v>-5383.0349999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D25">
         <v>46</v>
@@ -1618,27 +1469,21 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M25" t="s">
-        <v>40</v>
-      </c>
-      <c r="S25" s="1">
-        <v>17089</v>
-      </c>
-      <c r="T25" s="1">
-        <v>-1862.7010000000009</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D26">
         <v>15</v>
@@ -1655,27 +1500,21 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M26" t="s">
-        <v>40</v>
-      </c>
-      <c r="S26" s="1">
-        <v>8135.8499999999995</v>
-      </c>
-      <c r="T26" s="1">
-        <v>-2451.9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D27">
         <v>17</v>
@@ -1692,27 +1531,21 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
       <c r="L27" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M27" t="s">
-        <v>40</v>
-      </c>
-      <c r="S27" s="1">
-        <v>9473.25</v>
-      </c>
-      <c r="T27" s="1">
-        <v>-323.35360000000026</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D28">
         <v>18</v>
@@ -1724,27 +1557,22 @@
         <v>165</v>
       </c>
       <c r="L28" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M28" t="s">
-        <v>84</v>
-      </c>
-      <c r="S28" s="1">
-        <v>28329.5</v>
-      </c>
-      <c r="T28" s="1">
-        <v>762.91239999999925</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>36</v>
-      </c>
-      <c r="S32" s="1">
+        <v>34</v>
+      </c>
+      <c r="C32" s="1">
         <v>50000</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M28" xr:uid="{ECD91B5D-5949-4A3E-9EBC-E276EA4CC067}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/AI_portfolio.xlsx
+++ b/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B6A6BD-CEB8-4CC3-91D4-4F34683000E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEAF987-7976-4C29-B197-DC468E003109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5DF95D75-B56A-4A28-A4FD-98A7C607935C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5DF95D75-B56A-4A28-A4FD-98A7C607935C}"/>
   </bookViews>
   <sheets>
     <sheet name="Total" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="85">
   <si>
     <t>Danske Bank A/S</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>Portfolio_Weight</t>
+  </si>
+  <si>
+    <t>Grundfos</t>
   </si>
 </sst>
 </file>
@@ -1563,6 +1566,29 @@
         <v>82</v>
       </c>
     </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29">
+        <v>260</v>
+      </c>
+      <c r="E29" s="2">
+        <v>637</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1662</v>
+      </c>
+      <c r="L29" t="s">
+        <v>33</v>
+      </c>
+      <c r="M29" t="s">
+        <v>82</v>
+      </c>
+    </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>34</v>

--- a/AI_portfolio.xlsx
+++ b/AI_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEAF987-7976-4C29-B197-DC468E003109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7871F5A-1A14-4916-992C-52C1E5BA8863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5DF95D75-B56A-4A28-A4FD-98A7C607935C}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="86">
   <si>
     <t>Danske Bank A/S</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>Grundfos</t>
+  </si>
+  <si>
+    <t>Depot</t>
   </si>
 </sst>
 </file>
@@ -1573,6 +1576,9 @@
       <c r="B29" t="s">
         <v>84</v>
       </c>
+      <c r="C29" t="s">
+        <v>84</v>
+      </c>
       <c r="D29">
         <v>260</v>
       </c>
@@ -1586,7 +1592,7 @@
         <v>33</v>
       </c>
       <c r="M29" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">

--- a/AI_portfolio.xlsx
+++ b/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7871F5A-1A14-4916-992C-52C1E5BA8863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546DBD93-C809-444D-98F3-CFEA4C046687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5DF95D75-B56A-4A28-A4FD-98A7C607935C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5DF95D75-B56A-4A28-A4FD-98A7C607935C}"/>
   </bookViews>
   <sheets>
     <sheet name="Total" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="87">
   <si>
     <t>Danske Bank A/S</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>Depot</t>
+  </si>
+  <si>
+    <t>Medtag_i_vægt</t>
   </si>
 </sst>
 </file>
@@ -678,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD91B5D-5949-4A3E-9EBC-E276EA4CC067}">
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
@@ -696,7 +699,7 @@
     <col min="13" max="13" width="8.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>69</v>
       </c>
@@ -736,8 +739,11 @@
       <c r="M1" s="3" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N1" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -767,8 +773,11 @@
       <c r="M2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -798,8 +807,11 @@
       <c r="M3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>70</v>
       </c>
@@ -829,8 +841,11 @@
       <c r="M4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>70</v>
       </c>
@@ -860,8 +875,11 @@
       <c r="M5" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>70</v>
       </c>
@@ -891,8 +909,11 @@
       <c r="M6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>70</v>
       </c>
@@ -922,8 +943,11 @@
       <c r="M7" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>70</v>
       </c>
@@ -953,8 +977,11 @@
       <c r="M8" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>70</v>
       </c>
@@ -984,8 +1011,11 @@
       <c r="M9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>70</v>
       </c>
@@ -1015,8 +1045,11 @@
       <c r="M10" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -1046,8 +1079,11 @@
       <c r="M11" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>70</v>
       </c>
@@ -1077,8 +1113,11 @@
       <c r="M12" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>70</v>
       </c>
@@ -1108,8 +1147,11 @@
       <c r="M13" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -1139,8 +1181,11 @@
       <c r="M14" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>71</v>
       </c>
@@ -1170,8 +1215,11 @@
       <c r="M15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>71</v>
       </c>
@@ -1201,8 +1249,11 @@
       <c r="M16" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>71</v>
       </c>
@@ -1232,8 +1283,11 @@
       <c r="M17" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>71</v>
       </c>
@@ -1263,8 +1317,11 @@
       <c r="M18" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>71</v>
       </c>
@@ -1294,8 +1351,11 @@
       <c r="M19" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -1325,8 +1385,11 @@
       <c r="M20" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -1356,8 +1419,11 @@
       <c r="M21" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>71</v>
       </c>
@@ -1387,8 +1453,11 @@
       <c r="M22" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>71</v>
       </c>
@@ -1418,8 +1487,11 @@
       <c r="M23" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>71</v>
       </c>
@@ -1449,8 +1521,11 @@
       <c r="M24" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -1480,8 +1555,11 @@
       <c r="M25" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>71</v>
       </c>
@@ -1511,8 +1589,11 @@
       <c r="M26" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>71</v>
       </c>
@@ -1542,8 +1623,11 @@
       <c r="M27" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>71</v>
       </c>
@@ -1568,8 +1652,11 @@
       <c r="M28" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -1594,12 +1681,15 @@
       <c r="M29" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B32" t="s">
+      <c r="N29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B34" t="s">
         <v>34</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C34" s="1">
         <v>50000</v>
       </c>
     </row>

--- a/AI_portfolio.xlsx
+++ b/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546DBD93-C809-444D-98F3-CFEA4C046687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C24B88E0-691C-4157-A487-2CDFA4A44E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5DF95D75-B56A-4A28-A4FD-98A7C607935C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5DF95D75-B56A-4A28-A4FD-98A7C607935C}"/>
   </bookViews>
   <sheets>
     <sheet name="Total" sheetId="4" r:id="rId1"/>
@@ -1670,7 +1670,7 @@
         <v>260</v>
       </c>
       <c r="E29" s="2">
-        <v>637</v>
+        <v>606</v>
       </c>
       <c r="F29" s="2">
         <v>1662</v>
@@ -1684,6 +1684,12 @@
       <c r="N29" t="b">
         <v>0</v>
       </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="G31" s="1"/>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B34" t="s">

--- a/AI_portfolio.xlsx
+++ b/AI_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C24B88E0-691C-4157-A487-2CDFA4A44E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18C895B-5B0D-46B1-8D7A-A77EBD36EF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5DF95D75-B56A-4A28-A4FD-98A7C607935C}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Total!$A$1:$M$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -760,7 +759,7 @@
         <v>858.39</v>
       </c>
       <c r="F2" s="2">
-        <v>962.2</v>
+        <v>955.4</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -794,7 +793,7 @@
         <v>436.48</v>
       </c>
       <c r="F3" s="2">
-        <v>616.5</v>
+        <v>607.5</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -828,7 +827,7 @@
         <v>1018.6</v>
       </c>
       <c r="F4" s="2">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -862,7 +861,7 @@
         <v>200.16</v>
       </c>
       <c r="F5" s="2">
-        <v>366</v>
+        <v>357.3</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -896,7 +895,7 @@
         <v>40.619999999999997</v>
       </c>
       <c r="F6" s="2">
-        <v>37.64</v>
+        <v>38.130000000000003</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -930,7 +929,7 @@
         <v>388.08</v>
       </c>
       <c r="F7" s="2">
-        <v>350</v>
+        <v>336.2</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -964,7 +963,7 @@
         <v>405.68</v>
       </c>
       <c r="F8" s="2">
-        <v>916.5</v>
+        <v>890.5</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -992,13 +991,13 @@
         <v>49</v>
       </c>
       <c r="D9">
-        <v>436</v>
+        <v>336</v>
       </c>
       <c r="E9" s="2">
-        <v>443</v>
+        <v>426.68</v>
       </c>
       <c r="F9" s="2">
-        <v>321.39999999999998</v>
+        <v>317.35000000000002</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -1032,7 +1031,7 @@
         <v>631.61</v>
       </c>
       <c r="F10" s="2">
-        <v>759.6</v>
+        <v>752.8</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -1066,7 +1065,7 @@
         <v>144.16999999999999</v>
       </c>
       <c r="F11" s="2">
-        <v>157.97999999999999</v>
+        <v>150.04</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -1100,7 +1099,7 @@
         <v>414.2</v>
       </c>
       <c r="F12" s="2">
-        <v>418.74</v>
+        <v>415.84</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -1134,7 +1133,7 @@
         <v>366.4</v>
       </c>
       <c r="F13" s="2">
-        <v>381.8</v>
+        <v>371.6</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -1168,7 +1167,7 @@
         <v>145.84</v>
       </c>
       <c r="F14" s="2">
-        <v>178.85</v>
+        <v>174.5</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -1196,13 +1195,13 @@
         <v>55</v>
       </c>
       <c r="D15">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2">
-        <v>60.82</v>
+        <v>58.79</v>
       </c>
       <c r="F15" s="2">
-        <v>54</v>
+        <v>54.16</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -1230,13 +1229,13 @@
         <v>56</v>
       </c>
       <c r="D16">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E16" s="2">
-        <v>43.5</v>
+        <v>44.308</v>
       </c>
       <c r="F16" s="2">
-        <v>46</v>
+        <v>47.48</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -1267,7 +1266,7 @@
         <v>52</v>
       </c>
       <c r="E17" s="2">
-        <v>29</v>
+        <v>28.96</v>
       </c>
       <c r="F17" s="2">
         <v>22</v>
@@ -1301,10 +1300,10 @@
         <v>185</v>
       </c>
       <c r="E18" s="2">
-        <v>10.6</v>
+        <v>10.622</v>
       </c>
       <c r="F18" s="2">
-        <v>9</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -1372,7 +1371,7 @@
         <v>114.15900000000001</v>
       </c>
       <c r="F20" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -1406,7 +1405,7 @@
         <v>8.6419999999999995</v>
       </c>
       <c r="F21" s="2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -1437,10 +1436,10 @@
         <v>44</v>
       </c>
       <c r="E22" s="2">
-        <v>57.12</v>
+        <v>56.9</v>
       </c>
       <c r="F22" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -1505,7 +1504,7 @@
         <v>161</v>
       </c>
       <c r="E24" s="2">
-        <v>16.5</v>
+        <v>16.594000000000001</v>
       </c>
       <c r="F24" s="2">
         <v>12</v>
@@ -1542,7 +1541,7 @@
         <v>55.45</v>
       </c>
       <c r="F25" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -1573,10 +1572,10 @@
         <v>15</v>
       </c>
       <c r="E26" s="2">
-        <v>95</v>
+        <v>95.08</v>
       </c>
       <c r="F26" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -1610,7 +1609,7 @@
         <v>77.56</v>
       </c>
       <c r="F27" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -1644,7 +1643,7 @@
         <v>159</v>
       </c>
       <c r="F28">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L28" t="s">
         <v>40</v>

--- a/AI_portfolio.xlsx
+++ b/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18C895B-5B0D-46B1-8D7A-A77EBD36EF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA741A1C-6258-4FD3-981C-2473E5BA6784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5DF95D75-B56A-4A28-A4FD-98A7C607935C}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5DF95D75-B56A-4A28-A4FD-98A7C607935C}"/>
   </bookViews>
   <sheets>
     <sheet name="Total" sheetId="4" r:id="rId1"/>
@@ -683,7 +683,7 @@
   <dimension ref="A1:N34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="44.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.7265625" customWidth="1"/>
@@ -695,7 +695,8 @@
     <col min="10" max="10" width="10.7265625" customWidth="1"/>
     <col min="11" max="11" width="15.26953125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
@@ -1201,7 +1202,7 @@
         <v>58.79</v>
       </c>
       <c r="F15" s="2">
-        <v>54.16</v>
+        <v>53.5</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -1235,7 +1236,7 @@
         <v>44.308</v>
       </c>
       <c r="F16" s="2">
-        <v>47.48</v>
+        <v>47.4</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -1269,7 +1270,7 @@
         <v>28.96</v>
       </c>
       <c r="F17" s="2">
-        <v>22</v>
+        <v>21.2</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -1337,7 +1338,7 @@
         <v>9.6199999999999992</v>
       </c>
       <c r="F19" s="2">
-        <v>18</v>
+        <v>17.27</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -1371,7 +1372,7 @@
         <v>114.15900000000001</v>
       </c>
       <c r="F20" s="2">
-        <v>107</v>
+        <v>103.9</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -1405,7 +1406,7 @@
         <v>8.6419999999999995</v>
       </c>
       <c r="F21" s="2">
-        <v>8.5</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -1439,7 +1440,7 @@
         <v>56.9</v>
       </c>
       <c r="F22" s="2">
-        <v>53</v>
+        <v>52.7</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -1473,7 +1474,7 @@
         <v>27.972000000000001</v>
       </c>
       <c r="F23" s="2">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -1507,7 +1508,7 @@
         <v>16.594000000000001</v>
       </c>
       <c r="F24" s="2">
-        <v>12</v>
+        <v>11.77</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -1541,7 +1542,7 @@
         <v>55.45</v>
       </c>
       <c r="F25" s="2">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -1575,7 +1576,7 @@
         <v>95.08</v>
       </c>
       <c r="F26" s="2">
-        <v>72</v>
+        <v>68.900000000000006</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -1609,7 +1610,7 @@
         <v>77.56</v>
       </c>
       <c r="F27" s="2">
-        <v>76</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -1642,8 +1643,8 @@
       <c r="E28">
         <v>159</v>
       </c>
-      <c r="F28">
-        <v>164</v>
+      <c r="F28" s="2">
+        <v>163.5</v>
       </c>
       <c r="L28" t="s">
         <v>40</v>
